--- a/outputs/Block2_National_Final_Tuning_v12.xlsx
+++ b/outputs/Block2_National_Final_Tuning_v12.xlsx
@@ -495,7 +495,7 @@
         <v>22</v>
       </c>
       <c r="F2">
-        <v>0.02325119999999975</v>
+        <v>0.02325119999999976</v>
       </c>
       <c r="G2" t="s">
         <v>25</v>
@@ -633,7 +633,7 @@
         <v>22</v>
       </c>
       <c r="F8">
-        <v>0.03054480000000003</v>
+        <v>0.03054480000000005</v>
       </c>
       <c r="G8" t="s">
         <v>25</v>
@@ -702,7 +702,7 @@
         <v>22</v>
       </c>
       <c r="F11">
-        <v>0.03134800000000004</v>
+        <v>0.03134800000000005</v>
       </c>
       <c r="G11" t="s">
         <v>25</v>
